--- a/extenbooks/S1403_extenbook.xlsx
+++ b/extenbooks/S1403_extenbook.xlsx
@@ -8380,7 +8380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A103"/>
+  <dimension ref="A1:A105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -8412,414 +8412,414 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>**Data Provenance Record (DPR)** · **Phase 5** · **Ch 14** · **Fig 14.12**</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>## 1. Definition</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Quarterly HP(100)-filtered phase plot: y = wage share (W209RC1/GDP quarterly),</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>x = unemployment intensity (UNRATE * duration_index/100, monthly aggregated</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>to quarterly, duration rebased to 1948Q1-1951Q4 mean).</t>
+          <t>Quarterly HP(100)-filtered phase plot: y = wage share (W209RC1/GDP quarterly),</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>x = unemployment intensity (UNRATE * duration_index/100, monthly aggregated</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>## 2. Why it matters</t>
+          <t>to quarterly, duration rebased to 1948Q1-1951Q4 mean).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fig 14.12 is Shaikh's empirical analogue of the theoretical Goodwin-type</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>clockwise spiral in Fig 14.9 -- evidence that the Classical wage-share</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Phillips dynamic operates at quarterly frequency in real US data.</t>
+          <t>Fig 14.12 is Shaikh's empirical analogue of the theoretical Goodwin-type</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>clockwise spiral in Fig 14.9 -- evidence that the Classical wage-share</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>Phillips dynamic operates at quarterly frequency in real US data.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>| Subseries | Coverage | Source | Native units |</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>| S1403-A | 1948-2011 annual | Appendix 14.3 `wageshhp100` (reference axis) | decimal HP100 |</t>
+          <t>| Subseries | Coverage | Source | Native units |</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| S1403-B | 1948-2011 annual | Appendix 14.3 `ulintensityhp100` (reference axis) | decimal HP100 |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>| S1403-WSH_ANNUALAVG_HP100 | quarterly (collapsed to annual means) | FRED `W209RC1`/`GDP` quarterly, HP100-filtered, annual mean | decimal |</t>
+          <t>| S1403-A | 1948-2011 annual | Appendix 14.3 `wageshhp100` (reference axis) | decimal HP100 |</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>| S1403-ULINT_ANNUALAVG_HP100 | quarterly (collapsed to annual means) | FRED `UNRATE`+`UEMPMEAN` monthly→quarterly, HP100-filtered, annual mean | decimal |</t>
+          <t>| S1403-B | 1948-2011 annual | Appendix 14.3 `ulintensityhp100` (reference axis) | decimal HP100 |</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>| (sidecar) `S1403_quarterly.parquet` | quarterly long-form | Same as above | decimal |</t>
+          <t>| S1403-WSH_ANNUALAVG_HP100 | quarterly (collapsed to annual means) | FRED `W209RC1`/`GDP` quarterly, HP100-filtered, annual mean | decimal |</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>| S1403-ULINT_ANNUALAVG_HP100 | quarterly (collapsed to annual means) | FRED `UNRATE`+`UEMPMEAN` monthly→quarterly, HP100-filtered, annual mean | decimal |</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>| (sidecar) `S1403_quarterly.parquet` | quarterly long-form | Same as above | decimal |</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Phase 4 Q1 resolution:</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1. Fetch quarterly FRED `W209RC1` (Compensation of employees, paid: Domestic</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   industries, billions USD SAAR) and `GDP` (billions USD SAAR). Compute</t>
+          <t>Phase 4 Q1 resolution:</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   quarterly wage_share = W209RC1 / GDP.</t>
+          <t>1. Fetch quarterly FRED `W209RC1` (Compensation of employees, paid: Domestic</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2. Fetch monthly FRED `UNRATE` and `UEMPMEAN`. Aggregate to quarterly means.</t>
+          <t xml:space="preserve">   industries, billions USD SAAR) and `GDP` (billions USD SAAR). Compute</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Rebase duration to the 1948Q1-1951Q4 (16-quarter) mean of UEMPMEAN.</t>
+          <t xml:space="preserve">   quarterly wage_share = W209RC1 / GDP.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Intensity_q = (UNRATE_q/100) * (duration_index_q).</t>
+          <t>2. Fetch monthly FRED `UNRATE` and `UEMPMEAN`. Aggregate to quarterly means.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3. Apply HP filter with **lambda=100** (Shaikh's choice; NOT 1600) over the</t>
+          <t xml:space="preserve">   Rebase duration to the 1948Q1-1951Q4 (16-quarter) mean of UEMPMEAN.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">   full quarterly sample to both series independently.</t>
+          <t xml:space="preserve">   Intensity_q = (UNRATE_q/100) * (duration_index_q).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4. Collapse to annual means for the canonical processed parquet; preserve</t>
+          <t>3. Apply HP filter with **lambda=100** (Shaikh's choice; NOT 1600) over the</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">   quarterly data in a sidecar parquet for phase-plot visualization.</t>
+          <t xml:space="preserve">   full quarterly sample to both series independently.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4. Collapse to annual means for the canonical processed parquet; preserve</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t xml:space="preserve">   quarterly data in a sidecar parquet for phase-plot visualization.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Annual reference axes: 1948-2011 (Appendix). Quarterly phase plot:</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1948Q1-2024Q4 (FRED-derived).</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Annual reference axes: 1948-2011 (Appendix). Quarterly phase plot:</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>1948Q1-2024Q4 (FRED-derived).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>## 6. Units</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Decimal HP(100) values on both axes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>Decimal HP(100) values on both axes.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1. **HP lambda=100 for quarterly**: Shaikh deviates from the textbook</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   quarterly value of 1600. Per Appendix 14.2 p. 893, lambda=100 throughout.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   DO NOT substitute; the chosen lambda preserves the "zigs and zags" of</t>
+          <t>1. **HP lambda=100 for quarterly**: Shaikh deviates from the textbook</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">   intra-year dynamics that the phase plot relies upon.</t>
+          <t xml:space="preserve">   quarterly value of 1600. Per Appendix 14.2 p. 893, lambda=100 throughout.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2. **W270RE1Q156NBEA retired** (HTTP 404). Substituted W209RC1 + GDP</t>
+          <t xml:space="preserve">   DO NOT substitute; the chosen lambda preserves the "zigs and zags" of</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   quarterly pair (within-FRED ID routing; same NIPA T1.10 line 2 / line 1</t>
+          <t xml:space="preserve">   intra-year dynamics that the phase plot relies upon.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">   inputs). Not a concept change.</t>
+          <t>2. **W270RE1Q156NBEA retired** (HTTP 404). Substituted W209RC1 + GDP</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3. **Quarterly axes vs annual axes**: the FRED-derived axes collapsed to</t>
+          <t xml:space="preserve">   quarterly pair (within-FRED ID routing; same NIPA T1.10 line 2 / line 1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">   annual means differ modestly from Appendix annual HP100 axes because</t>
+          <t xml:space="preserve">   inputs). Not a concept change.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">   HP(annual mean of quarterly) ≠ annual mean of HP(quarterly). This is</t>
+          <t>3. **Quarterly axes vs annual axes**: the FRED-derived axes collapsed to</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">   reported informationally in the validator, not failed.</t>
+          <t xml:space="preserve">   annual means differ modestly from Appendix annual HP100 axes because</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   HP(annual mean of quarterly) ≠ annual mean of HP(quarterly). This is</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t xml:space="preserve">   reported informationally in the validator, not failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>## 8. Cross-references</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>CD legacy `S070`. Book p. 666; Appendix 14.2 p. 892-893.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>CD legacy `S070`. Book p. 666; Appendix 14.2 p. 892-893.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Tolerance ±1.0% for the annual reference axes (pass-through). Quarterly</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Tolerance ±1.0% for the annual reference axes (pass-through). Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>axes are informational (no Appendix truth to compare).</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4">
+    <row r="71">
+      <c r="A71" s="4">
         <f>== EPR: S1403_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t># S1403 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-    </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>**Series**: S1403 (Wage Share vs Unemployment Intensity) · **Ch 14** · **Authored**: 2026-05-18</t>
+          <t># S1403 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -8829,188 +8829,198 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>## Classification</t>
+          <t>**Series**: S1403 (Wage Share vs Unemployment Intensity) · **Ch 14** · **Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>`content_type: time_series` · `construction: composite` · extension applies via</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>re-derivation at quarterly frequency.</t>
+          <t>## Classification</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>`content_type: time_series` · `construction: composite` · extension applies via</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>## Method</t>
+          <t>re-derivation at quarterly frequency.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>HP100 is applied to the FULL extended quarterly sample (1948Q1-2024Q4), not</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>appended to the original-window filter output. This avoids endpoint bias on</t>
+          <t>## Method</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>the post-2011 segment.</t>
+          <t>HP100 is applied to the FULL extended quarterly sample (1948Q1-2024Q4), not</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>appended to the original-window filter output. This avoids endpoint bias on</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>## No-Proxy disclosure</t>
+          <t>the post-2011 segment.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>The dead FRED ID `W270RE1Q156NBEA` is replaced by the live pair `W209RC1` +</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>`GDP` at quarterly frequency. This is a within-FRED routing update to the</t>
+          <t>## No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SAME underlying NIPA Table 1.10 line 2 / line 1 series; not a concept-changing</t>
+          <t>The dead FRED ID `W270RE1Q156NBEA` is replaced by the live pair `W209RC1` +</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>substitution. No `proxy: true` flag required.</t>
+          <t>`GDP` at quarterly frequency. This is a within-FRED routing update to the</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SAME underlying NIPA Table 1.10 line 2 / line 1 series; not a concept-changing</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>## No-Synthetic disclosure</t>
+          <t>substitution. No `proxy: true` flag required.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>All quarterly observations are primary BEA/BLS data. HP filtering is the</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>documented analytical method per Shaikh's Appendix 14.2.</t>
+          <t>## No-Synthetic disclosure</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>All quarterly observations are primary BEA/BLS data. HP filtering is the</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>## Failure-mode table</t>
+          <t>documented analytical method per Shaikh's Appendix 14.2.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>| Mode | Trigger | Behaviour |</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>## Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>| FRED key missing | env unset | Quarterly axes skipped; annual reference axes still emitted |</t>
+          <t>| Mode | Trigger | Behaviour |</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>| One quarterly source missing | API outage | Quarterly axes skipped; annual reference axes still emitted |</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>| HP lambda substitution | maintainer error | Caught by Shaikh-specific test (HP_LAMBDA_CH14=100 constant) |</t>
+          <t>| FRED key missing | env unset | Quarterly axes skipped; annual reference axes still emitted |</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>| One quarterly source missing | API outage | Quarterly axes skipped; annual reference axes still emitted |</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>## CD2 divergence pre-disclosure</t>
+          <t>| HP lambda substitution | maintainer error | Caught by Shaikh-specific test (HP_LAMBDA_CH14=100 constant) |</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Minor (&lt;2%) divergence expected on the quarterly axes vs CD2 because CD2 used</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>the now-retired W270RE1Q156NBEA and a different quarterly aggregation</t>
+          <t>## CD2 divergence pre-disclosure</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
+        <is>
+          <t>Minor (&lt;2%) divergence expected on the quarterly axes vs CD2 because CD2 used</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>the now-retired W270RE1Q156NBEA and a different quarterly aggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>convention.</t>
         </is>
@@ -9479,11 +9489,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9506,76 +9516,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Wage Share vs Unemployment Intensity (Empirical Spiral)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1403_research.json", "adequacy_report": "Technical/docs/chapters/CH14_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1403_DPR.md", "epr": "Technical/docs/series/S1403_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1403_load.py", "processor": "Technical/code/P02_processors/P02_S1403_construct.py", "validator": "Technical/code/V03_validators/V03_S1403_validate.py", "processed": "Technical/data/processed/S1403.parquet", "chopped_csv": "Technical/chopped/S1403.csv", "extenbook_xlsx": "Technical/extenbooks/S1403_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:58:43.529185+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1403_extenbook.xlsx
+++ b/extenbooks/S1403_extenbook.xlsx
@@ -927,7 +927,7 @@
         <v>0.08084174099779408</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5496116982382457</v>
+        <v>0.549611698238244</v>
       </c>
     </row>
     <row r="16">
@@ -944,7 +944,7 @@
         <v>0.08381398013403929</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5525873892552928</v>
+        <v>0.5525873892552936</v>
       </c>
     </row>
     <row r="17">
@@ -961,7 +961,7 @@
         <v>0.08924152538679307</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5525990196850911</v>
+        <v>0.5525990196850924</v>
       </c>
     </row>
     <row r="18">
@@ -978,7 +978,7 @@
         <v>0.08636265398535865</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5508305763972181</v>
+        <v>0.5508305763972189</v>
       </c>
     </row>
     <row r="19">
@@ -995,7 +995,7 @@
         <v>0.07776490326280508</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5491339536435059</v>
+        <v>0.5491339536435074</v>
       </c>
     </row>
     <row r="20">
@@ -1012,7 +1012,7 @@
         <v>0.06633076997737289</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5480274310428088</v>
+        <v>0.5480274310428103</v>
       </c>
     </row>
     <row r="21">
@@ -1029,7 +1029,7 @@
         <v>0.05283919945031241</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5484604363706163</v>
+        <v>0.5484604363706161</v>
       </c>
     </row>
     <row r="22">
@@ -1046,7 +1046,7 @@
         <v>0.04046861521223587</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5523756464094639</v>
+        <v>0.5523756464094628</v>
       </c>
     </row>
     <row r="23">
@@ -1063,7 +1063,7 @@
         <v>0.03229084076076789</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5589783859179227</v>
+        <v>0.5589783859179204</v>
       </c>
     </row>
     <row r="24">
@@ -1097,7 +1097,7 @@
         <v>0.03279380721206751</v>
       </c>
       <c r="E25" t="n">
-        <v>0.573457589156369</v>
+        <v>0.5734575891563708</v>
       </c>
     </row>
     <row r="26">
@@ -1114,7 +1114,7 @@
         <v>0.04514353179677996</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5764615220569144</v>
+        <v>0.5764615220569146</v>
       </c>
     </row>
     <row r="27">
@@ -1131,7 +1131,7 @@
         <v>0.05753339981353545</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5745130435995545</v>
+        <v>0.574513043599556</v>
       </c>
     </row>
     <row r="28">
@@ -1148,7 +1148,7 @@
         <v>0.05950860989326576</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5724338978025391</v>
+        <v>0.5724338978025442</v>
       </c>
     </row>
     <row r="29">
@@ -1165,7 +1165,7 @@
         <v>0.05857173359541064</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5714922273670628</v>
+        <v>0.5714922273670663</v>
       </c>
     </row>
     <row r="30">
@@ -1182,7 +1182,7 @@
         <v>0.07341227932339854</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5695785864642255</v>
+        <v>0.5695785864642252</v>
       </c>
     </row>
     <row r="31">
@@ -1199,7 +1199,7 @@
         <v>0.1010862775290277</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5646035554049332</v>
+        <v>0.5646035554049342</v>
       </c>
     </row>
     <row r="32">
@@ -1216,7 +1216,7 @@
         <v>0.1119362838058277</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5606984211384247</v>
+        <v>0.5606984211384279</v>
       </c>
     </row>
     <row r="33">
@@ -1233,7 +1233,7 @@
         <v>0.09829964355367031</v>
       </c>
       <c r="E33" t="n">
-        <v>0.55991157275109</v>
+        <v>0.5599115727510939</v>
       </c>
     </row>
     <row r="34">
@@ -1250,7 +1250,7 @@
         <v>0.07744364305169076</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5607586129700741</v>
+        <v>0.5607586129700777</v>
       </c>
     </row>
     <row r="35">
@@ -1284,7 +1284,7 @@
         <v>0.08362512609489028</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5642088385351881</v>
+        <v>0.5642088385351856</v>
       </c>
     </row>
     <row r="37">
@@ -1301,7 +1301,7 @@
         <v>0.113503606170327</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5634859512137496</v>
+        <v>0.5634859512137459</v>
       </c>
     </row>
     <row r="38">
@@ -1318,7 +1318,7 @@
         <v>0.1486872065656292</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5608962936453483</v>
+        <v>0.560896293645346</v>
       </c>
     </row>
     <row r="39">
@@ -1335,7 +1335,7 @@
         <v>0.1637040266559612</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5551863884441884</v>
+        <v>0.5551863884441895</v>
       </c>
     </row>
     <row r="40">
@@ -1352,7 +1352,7 @@
         <v>0.1454807273575048</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5507391557664613</v>
+        <v>0.5507391557664633</v>
       </c>
     </row>
     <row r="41">
@@ -1369,7 +1369,7 @@
         <v>0.1198275317452303</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5511052247888617</v>
+        <v>0.5511052247888635</v>
       </c>
     </row>
     <row r="42">
@@ -1386,7 +1386,7 @@
         <v>0.1013996551171857</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5551038811172175</v>
+        <v>0.5551038811172173</v>
       </c>
     </row>
     <row r="43">
@@ -1403,7 +1403,7 @@
         <v>0.08597978034432266</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5592487643922522</v>
+        <v>0.559248764392251</v>
       </c>
     </row>
     <row r="44">
@@ -1420,7 +1420,7 @@
         <v>0.07196070179357582</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5605162498002166</v>
+        <v>0.5605162498002164</v>
       </c>
     </row>
     <row r="45">
@@ -1437,7 +1437,7 @@
         <v>0.06537263779287206</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5596741821229337</v>
+        <v>0.559674182122935</v>
       </c>
     </row>
     <row r="46">
@@ -1454,7 +1454,7 @@
         <v>0.07375653189007174</v>
       </c>
       <c r="E46" t="n">
-        <v>0.560069588238836</v>
+        <v>0.5600695882388371</v>
       </c>
     </row>
     <row r="47">
@@ -1471,7 +1471,7 @@
         <v>0.09636221854205303</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5610155030538418</v>
+        <v>0.5610155030538426</v>
       </c>
     </row>
     <row r="48">
@@ -1488,7 +1488,7 @@
         <v>0.1183114386742482</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5601086962589958</v>
+        <v>0.5601086962589968</v>
       </c>
     </row>
     <row r="49">
@@ -1505,7 +1505,7 @@
         <v>0.1231197155664469</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5562320801845916</v>
+        <v>0.556232080184591</v>
       </c>
     </row>
     <row r="50">
@@ -1522,7 +1522,7 @@
         <v>0.1130526266830223</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5515450550542089</v>
+        <v>0.5515450550542085</v>
       </c>
     </row>
     <row r="51">
@@ -1539,7 +1539,7 @@
         <v>0.09873267115392832</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5485355682410707</v>
+        <v>0.5485355682410722</v>
       </c>
     </row>
     <row r="52">
@@ -1556,7 +1556,7 @@
         <v>0.08701455504850193</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5479969285747139</v>
+        <v>0.5479969285747142</v>
       </c>
     </row>
     <row r="53">
@@ -1573,7 +1573,7 @@
         <v>0.07561068758376221</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5511264743523074</v>
+        <v>0.5511264743523029</v>
       </c>
     </row>
     <row r="54">
@@ -1590,7 +1590,7 @@
         <v>0.06386119252124973</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5573926065957341</v>
+        <v>0.5573926065957265</v>
       </c>
     </row>
     <row r="55">
@@ -1607,7 +1607,7 @@
         <v>0.05495100088877337</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5637309370557473</v>
+        <v>0.5637309370557584</v>
       </c>
     </row>
     <row r="56">
@@ -1624,7 +1624,7 @@
         <v>0.05456149059025892</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5683290271301684</v>
+        <v>0.5683290271302602</v>
       </c>
     </row>
     <row r="57">
@@ -1641,7 +1641,7 @@
         <v>0.0684968197490885</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5678930808784303</v>
+        <v>0.5678930808786763</v>
       </c>
     </row>
     <row r="58">
@@ -1658,7 +1658,7 @@
         <v>0.09154736482315623</v>
       </c>
       <c r="E58" t="n">
-        <v>0.562361632187552</v>
+        <v>0.5623616321877639</v>
       </c>
     </row>
     <row r="59">
@@ -1675,7 +1675,7 @@
         <v>0.1070526305303018</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5552412406749985</v>
+        <v>0.5552412406741671</v>
       </c>
     </row>
     <row r="60">
@@ -1692,7 +1692,7 @@
         <v>0.1050407680897334</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5488113690377918</v>
+        <v>0.5488113690339484</v>
       </c>
     </row>
     <row r="61">
@@ -1709,7 +1709,7 @@
         <v>0.09007156819178741</v>
       </c>
       <c r="E61" t="n">
-        <v>0.5442647759260872</v>
+        <v>0.5442647759192287</v>
       </c>
     </row>
     <row r="62">
@@ -1726,7 +1726,7 @@
         <v>0.07596613433262292</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5429834447507452</v>
+        <v>0.5429834447527181</v>
       </c>
     </row>
     <row r="63">
@@ -1743,7 +1743,7 @@
         <v>0.08247068269197647</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5433354832484214</v>
+        <v>0.5433354832958459</v>
       </c>
     </row>
     <row r="64">
@@ -1760,7 +1760,7 @@
         <v>0.1303616803517417</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5416323167383522</v>
+        <v>0.5416323168729024</v>
       </c>
     </row>
     <row r="65">
@@ -1777,7 +1777,7 @@
         <v>0.2185767722066536</v>
       </c>
       <c r="E65" t="n">
-        <v>0.5362738573134542</v>
+        <v>0.5362738574430939</v>
       </c>
     </row>
     <row r="66">
@@ -1794,7 +1794,7 @@
         <v>0.3003264255026281</v>
       </c>
       <c r="E66" t="n">
-        <v>0.530218159709627</v>
+        <v>0.5302181592990096</v>
       </c>
     </row>
     <row r="67">
@@ -1811,7 +1811,7 @@
         <v>0.3345631022652946</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5267641638258111</v>
+        <v>0.526764161776578</v>
       </c>
     </row>
     <row r="68">
@@ -1828,7 +1828,7 @@
         <v>0.3172546197791978</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5253829674277923</v>
+        <v>0.525382963574795</v>
       </c>
     </row>
     <row r="69">
@@ -1845,7 +1845,7 @@
         <v>0.2685442680305679</v>
       </c>
       <c r="E69" t="n">
-        <v>0.525086253538471</v>
+        <v>0.5250862539913828</v>
       </c>
     </row>
     <row r="70">
@@ -1862,7 +1862,7 @@
         <v>0.2104233975741044</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5260694677080567</v>
+        <v>0.5260694923279714</v>
       </c>
     </row>
     <row r="71">
@@ -1879,7 +1879,7 @@
         <v>0.1606055119112141</v>
       </c>
       <c r="E71" t="n">
-        <v>0.5283640738528323</v>
+        <v>0.5283641471458197</v>
       </c>
     </row>
     <row r="72">
@@ -1896,7 +1896,7 @@
         <v>0.1267480557734879</v>
       </c>
       <c r="E72" t="n">
-        <v>0.5300366554469729</v>
+        <v>0.5300367333844399</v>
       </c>
     </row>
     <row r="73">
@@ -1913,7 +1913,7 @@
         <v>0.1036676966180005</v>
       </c>
       <c r="E73" t="n">
-        <v>0.5310708832965731</v>
+        <v>0.531070682230663</v>
       </c>
     </row>
     <row r="74">
@@ -1930,7 +1930,7 @@
         <v>0.0915487132411911</v>
       </c>
       <c r="E74" t="n">
-        <v>0.5325557277409311</v>
+        <v>0.5325546371628782</v>
       </c>
     </row>
     <row r="75">
@@ -1947,7 +1947,7 @@
         <v>0.09856715783554884</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5349059100381952</v>
+        <v>0.5349037542886498</v>
       </c>
     </row>
     <row r="76">
@@ -1964,7 +1964,7 @@
         <v>0.1214607148468068</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5352228022640857</v>
+        <v>0.5352227183720457</v>
       </c>
     </row>
     <row r="77">
@@ -1981,7 +1981,7 @@
         <v>0.1248308115766403</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5287769736863975</v>
+        <v>0.5287897069984153</v>
       </c>
     </row>
     <row r="78">
@@ -1998,7 +1998,7 @@
         <v>0.09988927686788407</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5191958012959864</v>
+        <v>0.5192356254603154</v>
       </c>
     </row>
     <row r="79">
@@ -2015,7 +2015,7 @@
         <v>0.08219315623571952</v>
       </c>
       <c r="E79" t="n">
-        <v>0.5131362269648649</v>
+        <v>0.5131824563827045</v>
       </c>
     </row>
     <row r="80">
@@ -2032,7 +2032,7 @@
         <v>0.08397241740656292</v>
       </c>
       <c r="E80" t="n">
-        <v>0.5115855515814559</v>
+        <v>0.5114882872245341</v>
       </c>
     </row>
     <row r="81">
@@ -2049,7 +2049,7 @@
         <v>0.09597755326131424</v>
       </c>
       <c r="E81" t="n">
-        <v>0.5111362553532959</v>
+        <v>0.5105573002721118</v>
       </c>
     </row>
     <row r="82"/>
@@ -6832,7 +6832,7 @@
         <v>1959</v>
       </c>
       <c r="B293" t="n">
-        <v>0.5496116982382457</v>
+        <v>0.549611698238244</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>1960</v>
       </c>
       <c r="B294" t="n">
-        <v>0.5525873892552928</v>
+        <v>0.5525873892552936</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>1961</v>
       </c>
       <c r="B295" t="n">
-        <v>0.5525990196850911</v>
+        <v>0.5525990196850924</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>1962</v>
       </c>
       <c r="B296" t="n">
-        <v>0.5508305763972181</v>
+        <v>0.5508305763972189</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>1963</v>
       </c>
       <c r="B297" t="n">
-        <v>0.5491339536435059</v>
+        <v>0.5491339536435074</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>1964</v>
       </c>
       <c r="B298" t="n">
-        <v>0.5480274310428088</v>
+        <v>0.5480274310428103</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>1965</v>
       </c>
       <c r="B299" t="n">
-        <v>0.5484604363706163</v>
+        <v>0.5484604363706161</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>1966</v>
       </c>
       <c r="B300" t="n">
-        <v>0.5523756464094639</v>
+        <v>0.5523756464094628</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>1967</v>
       </c>
       <c r="B301" t="n">
-        <v>0.5589783859179227</v>
+        <v>0.5589783859179204</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>1969</v>
       </c>
       <c r="B303" t="n">
-        <v>0.573457589156369</v>
+        <v>0.5734575891563708</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>1970</v>
       </c>
       <c r="B304" t="n">
-        <v>0.5764615220569144</v>
+        <v>0.5764615220569146</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>1971</v>
       </c>
       <c r="B305" t="n">
-        <v>0.5745130435995545</v>
+        <v>0.574513043599556</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>1972</v>
       </c>
       <c r="B306" t="n">
-        <v>0.5724338978025391</v>
+        <v>0.5724338978025442</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>1973</v>
       </c>
       <c r="B307" t="n">
-        <v>0.5714922273670628</v>
+        <v>0.5714922273670663</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>1974</v>
       </c>
       <c r="B308" t="n">
-        <v>0.5695785864642255</v>
+        <v>0.5695785864642252</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>1975</v>
       </c>
       <c r="B309" t="n">
-        <v>0.5646035554049332</v>
+        <v>0.5646035554049342</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>1976</v>
       </c>
       <c r="B310" t="n">
-        <v>0.5606984211384247</v>
+        <v>0.5606984211384279</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>1977</v>
       </c>
       <c r="B311" t="n">
-        <v>0.55991157275109</v>
+        <v>0.5599115727510939</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>1978</v>
       </c>
       <c r="B312" t="n">
-        <v>0.5607586129700741</v>
+        <v>0.5607586129700777</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>1980</v>
       </c>
       <c r="B314" t="n">
-        <v>0.5642088385351881</v>
+        <v>0.5642088385351856</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>1981</v>
       </c>
       <c r="B315" t="n">
-        <v>0.5634859512137496</v>
+        <v>0.5634859512137459</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>1982</v>
       </c>
       <c r="B316" t="n">
-        <v>0.5608962936453483</v>
+        <v>0.560896293645346</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>1983</v>
       </c>
       <c r="B317" t="n">
-        <v>0.5551863884441884</v>
+        <v>0.5551863884441895</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>1984</v>
       </c>
       <c r="B318" t="n">
-        <v>0.5507391557664613</v>
+        <v>0.5507391557664633</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>1985</v>
       </c>
       <c r="B319" t="n">
-        <v>0.5511052247888617</v>
+        <v>0.5511052247888635</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>1986</v>
       </c>
       <c r="B320" t="n">
-        <v>0.5551038811172175</v>
+        <v>0.5551038811172173</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>1987</v>
       </c>
       <c r="B321" t="n">
-        <v>0.5592487643922522</v>
+        <v>0.559248764392251</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>1988</v>
       </c>
       <c r="B322" t="n">
-        <v>0.5605162498002166</v>
+        <v>0.5605162498002164</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>1989</v>
       </c>
       <c r="B323" t="n">
-        <v>0.5596741821229337</v>
+        <v>0.559674182122935</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>1990</v>
       </c>
       <c r="B324" t="n">
-        <v>0.560069588238836</v>
+        <v>0.5600695882388371</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>1991</v>
       </c>
       <c r="B325" t="n">
-        <v>0.5610155030538418</v>
+        <v>0.5610155030538426</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>1992</v>
       </c>
       <c r="B326" t="n">
-        <v>0.5601086962589958</v>
+        <v>0.5601086962589968</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>1993</v>
       </c>
       <c r="B327" t="n">
-        <v>0.5562320801845916</v>
+        <v>0.556232080184591</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>1994</v>
       </c>
       <c r="B328" t="n">
-        <v>0.5515450550542089</v>
+        <v>0.5515450550542085</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>1995</v>
       </c>
       <c r="B329" t="n">
-        <v>0.5485355682410707</v>
+        <v>0.5485355682410722</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>1996</v>
       </c>
       <c r="B330" t="n">
-        <v>0.5479969285747139</v>
+        <v>0.5479969285747142</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>1997</v>
       </c>
       <c r="B331" t="n">
-        <v>0.5511264743523074</v>
+        <v>0.5511264743523029</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>1998</v>
       </c>
       <c r="B332" t="n">
-        <v>0.5573926065957341</v>
+        <v>0.5573926065957265</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>1999</v>
       </c>
       <c r="B333" t="n">
-        <v>0.5637309370557473</v>
+        <v>0.5637309370557584</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>2000</v>
       </c>
       <c r="B334" t="n">
-        <v>0.5683290271301684</v>
+        <v>0.5683290271302602</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>2001</v>
       </c>
       <c r="B335" t="n">
-        <v>0.5678930808784303</v>
+        <v>0.5678930808786763</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>2002</v>
       </c>
       <c r="B336" t="n">
-        <v>0.562361632187552</v>
+        <v>0.5623616321877639</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>2003</v>
       </c>
       <c r="B337" t="n">
-        <v>0.5552412406749985</v>
+        <v>0.5552412406741671</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>2004</v>
       </c>
       <c r="B338" t="n">
-        <v>0.5488113690377918</v>
+        <v>0.5488113690339484</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>2005</v>
       </c>
       <c r="B339" t="n">
-        <v>0.5442647759260872</v>
+        <v>0.5442647759192287</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>2006</v>
       </c>
       <c r="B340" t="n">
-        <v>0.5429834447507452</v>
+        <v>0.5429834447527181</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>2007</v>
       </c>
       <c r="B341" t="n">
-        <v>0.5433354832484214</v>
+        <v>0.5433354832958459</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>2008</v>
       </c>
       <c r="B342" t="n">
-        <v>0.5416323167383522</v>
+        <v>0.5416323168729024</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>2009</v>
       </c>
       <c r="B343" t="n">
-        <v>0.5362738573134542</v>
+        <v>0.5362738574430939</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>2010</v>
       </c>
       <c r="B344" t="n">
-        <v>0.530218159709627</v>
+        <v>0.5302181592990096</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>2011</v>
       </c>
       <c r="B345" t="n">
-        <v>0.5267641638258111</v>
+        <v>0.526764161776578</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>2012</v>
       </c>
       <c r="B346" t="n">
-        <v>0.5253829674277923</v>
+        <v>0.525382963574795</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>2013</v>
       </c>
       <c r="B347" t="n">
-        <v>0.525086253538471</v>
+        <v>0.5250862539913828</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>2014</v>
       </c>
       <c r="B348" t="n">
-        <v>0.5260694677080567</v>
+        <v>0.5260694923279714</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>2015</v>
       </c>
       <c r="B349" t="n">
-        <v>0.5283640738528323</v>
+        <v>0.5283641471458197</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>2016</v>
       </c>
       <c r="B350" t="n">
-        <v>0.5300366554469729</v>
+        <v>0.5300367333844399</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>2017</v>
       </c>
       <c r="B351" t="n">
-        <v>0.5310708832965731</v>
+        <v>0.531070682230663</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>2018</v>
       </c>
       <c r="B352" t="n">
-        <v>0.5325557277409311</v>
+        <v>0.5325546371628782</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>2019</v>
       </c>
       <c r="B353" t="n">
-        <v>0.5349059100381952</v>
+        <v>0.5349037542886498</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>2020</v>
       </c>
       <c r="B354" t="n">
-        <v>0.5352228022640857</v>
+        <v>0.5352227183720457</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>2021</v>
       </c>
       <c r="B355" t="n">
-        <v>0.5287769736863975</v>
+        <v>0.5287897069984153</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>2022</v>
       </c>
       <c r="B356" t="n">
-        <v>0.5191958012959864</v>
+        <v>0.5192356254603154</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>2023</v>
       </c>
       <c r="B357" t="n">
-        <v>0.5131362269648649</v>
+        <v>0.5131824563827045</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>2024</v>
       </c>
       <c r="B358" t="n">
-        <v>0.5115855515814559</v>
+        <v>0.5114882872245341</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>2025</v>
       </c>
       <c r="B359" t="n">
-        <v>0.5111362553532959</v>
+        <v>0.5105573002721118</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A105"/>
+  <dimension ref="A1:A110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -8412,86 +8412,86 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Data Provenance Record** · **Ingestion stage** · **Chapter 14** · **Figure 14.12**</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>**Data Provenance Record (DPR)** · **Phase 5** · **Ch 14** · **Fig 14.12**</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Quarterly HP(100)-filtered (Hodrick-Prescott filter, smoothing parameter lambda=100) phase plot: y = wage share (W209RC1/GDP quarterly),</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>## 1. Definition</t>
+          <t>x = unemployment intensity (UNRATE * duration_index/100, monthly aggregated</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quarterly HP(100)-filtered phase plot: y = wage share (W209RC1/GDP quarterly),</t>
+          <t>to quarterly, duration rebased to 1948Q1-1951Q4 mean).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>x = unemployment intensity (UNRATE * duration_index/100, monthly aggregated</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>to quarterly, duration rebased to 1948Q1-1951Q4 mean).</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fig 14.12 is Shaikh's empirical analogue of the theoretical Goodwin-type</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>## 2. Why it matters</t>
+          <t>clockwise spiral in Fig 14.9 -- evidence that the Classical wage-share</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fig 14.12 is Shaikh's empirical analogue of the theoretical Goodwin-type</t>
+          <t>Phillips dynamic operates at quarterly frequency in real US data.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>clockwise spiral in Fig 14.9 -- evidence that the Classical wage-share</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Phillips dynamic operates at quarterly frequency in real US data.</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
@@ -8501,390 +8501,390 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1403-A, S1403-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>| Subseries | Coverage | Source | Native units |</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>| Subseries | Coverage | Source | Native units |</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>| S1403-A | 1948-2011 annual | Appendix 14.3 `wageshhp100` (reference axis) | decimal HP100 |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>| S1403-B | 1948-2011 annual | Appendix 14.3 `ulintensityhp100` (reference axis) | decimal HP100 |</t>
+          <t>| S1403-A | 1948-2011 annual | Appendix 14.3 `wageshhp100` (reference axis) | decimal HP100 |</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>| S1403-WSH_ANNUALAVG_HP100 | quarterly (collapsed to annual means) | FRED `W209RC1`/`GDP` quarterly, HP100-filtered, annual mean | decimal |</t>
+          <t>| S1403-B | 1948-2011 annual | Appendix 14.3 `ulintensityhp100` (reference axis) | decimal HP100 |</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>| S1403-ULINT_ANNUALAVG_HP100 | quarterly (collapsed to annual means) | FRED `UNRATE`+`UEMPMEAN` monthly→quarterly, HP100-filtered, annual mean | decimal |</t>
+          <t>| S1403-WSH_ANNUALAVG_HP100 | quarterly (collapsed to annual means) | FRED `W209RC1`/`GDP` quarterly, HP100-filtered, annual mean | decimal |</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>| S1403-ULINT_ANNUALAVG_HP100 | quarterly (collapsed to annual means) | FRED `UNRATE`+`UEMPMEAN` monthly→quarterly, HP100-filtered, annual mean | decimal |</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>| (sidecar) `S1403_quarterly.parquet` | quarterly long-form | Same as above | decimal |</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Phase 4 Q1 resolution:</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1. Fetch quarterly FRED `W209RC1` (Compensation of employees, paid: Domestic</t>
+          <t>Procedure (settled in the data-adequacy review):</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   industries, billions USD SAAR) and `GDP` (billions USD SAAR). Compute</t>
+          <t>1. Fetch quarterly FRED `W209RC1` (Compensation of employees, paid: Domestic</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">   quarterly wage_share = W209RC1 / GDP.</t>
+          <t xml:space="preserve">   industries, billions USD seasonally adjusted annual rate (SAAR)) and `GDP` (billions USD SAAR). Compute</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2. Fetch monthly FRED `UNRATE` and `UEMPMEAN`. Aggregate to quarterly means.</t>
+          <t xml:space="preserve">   quarterly wage_share = W209RC1 / GDP.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Rebase duration to the 1948Q1-1951Q4 (16-quarter) mean of UEMPMEAN.</t>
+          <t>2. Fetch monthly FRED `UNRATE` and `UEMPMEAN`. Aggregate to quarterly means.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Intensity_q = (UNRATE_q/100) * (duration_index_q).</t>
+          <t xml:space="preserve">   Rebase duration to the 1948Q1-1951Q4 (16-quarter) mean of UEMPMEAN.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3. Apply HP filter with **lambda=100** (Shaikh's choice; NOT 1600) over the</t>
+          <t xml:space="preserve">   Intensity_q = (UNRATE_q/100) * (duration_index_q).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">   full quarterly sample to both series independently.</t>
+          <t>3. Apply HP filter with **lambda=100** (Shaikh's choice; NOT 1600) over the</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4. Collapse to annual means for the canonical processed parquet; preserve</t>
+          <t xml:space="preserve">   full quarterly sample to both series independently.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>4. Collapse to annual means for the canonical processed parquet; preserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t xml:space="preserve">   quarterly data in a sidecar parquet for phase-plot visualization.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-    </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>## 5. Year coverage</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Annual reference axes: 1948-2011 (Appendix). Quarterly phase plot:</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>Annual reference axes: 1948-2011 (Appendix). Quarterly phase plot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>1948Q1-2024Q4 (FRED-derived).</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>## 6. Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Decimal HP(100) values on both axes.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1. **HP lambda=100 for quarterly**: Shaikh deviates from the textbook</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">   quarterly value of 1600. Per Appendix 14.2 p. 893, lambda=100 throughout.</t>
+          <t>1. **HP lambda=100 for quarterly**: Shaikh deviates from the textbook</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">   DO NOT substitute; the chosen lambda preserves the "zigs and zags" of</t>
+          <t xml:space="preserve">   quarterly value of 1600. Per Appendix 14.2 p. 893, lambda=100 throughout.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   intra-year dynamics that the phase plot relies upon.</t>
+          <t xml:space="preserve">   DO NOT substitute; the chosen lambda preserves the "zigs and zags" of</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2. **W270RE1Q156NBEA retired** (HTTP 404). Substituted W209RC1 + GDP</t>
+          <t xml:space="preserve">   intra-year dynamics that the phase plot relies upon.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">   quarterly pair (within-FRED ID routing; same NIPA T1.10 line 2 / line 1</t>
+          <t>2. **W270RE1Q156NBEA retired** (HTTP 404). Substituted W209RC1 + GDP</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">   inputs). Not a concept change.</t>
+          <t xml:space="preserve">   quarterly pair (within-FRED ID routing; same National Income and Product Accounts (NIPA) T1.10 line 2 / line 1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3. **Quarterly axes vs annual axes**: the FRED-derived axes collapsed to</t>
+          <t xml:space="preserve">   inputs). Not a concept change. FRED labels `W209RC1` "Compensation of</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">   annual means differ modestly from Appendix annual HP100 axes because</t>
+          <t xml:space="preserve">   employees, received" (NIPA Table 2.1); the book cites "paid" from NIPA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">   HP(annual mean of quarterly) ≠ annual mean of HP(quarterly). This is</t>
+          <t xml:space="preserve">   Table 1.10 line 2 — the same total-compensation aggregate, coincident in</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">   reported informationally in the validator, not failed.</t>
+          <t xml:space="preserve">   NIPA accounting (clarified 2026-07-01). Use `W209RC1`, not `A576RC1`</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (Wage &amp; Salary Disbursements only).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>3. **Quarterly axes vs annual axes**: the FRED-derived axes collapsed to</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CD legacy `S070`. Book p. 666; Appendix 14.2 p. 892-893.</t>
+          <t xml:space="preserve">   annual means differ modestly from Appendix annual HP100 axes because</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   HP(annual mean of quarterly) ≠ annual mean of HP(quarterly). This is</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t xml:space="preserve">   reported informationally in the validator, not failed.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Tolerance ±1.0% for the annual reference axes (pass-through). Quarterly</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Predecessor build: `S070`. Book p. 666; Appendix 14.2 p. 892-893.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tolerance ±1.0% for the annual reference axes (pass-through). Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>axes are informational (no Appendix truth to compare).</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4">
+    <row r="76">
+      <c r="A76" s="4">
         <f>== EPR: S1403_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t># S1403 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>**Series**: S1403 (Wage Share vs Unemployment Intensity) · **Ch 14** · **Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>## Classification</t>
-        </is>
-      </c>
-    </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>`content_type: time_series` · `construction: composite` · extension applies via</t>
+          <t># S1403 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>re-derivation at quarterly frequency.</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>**Series**: S1403 (Wage Share vs Unemployment Intensity) · **Chapter 14** · **Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>## Method</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HP100 is applied to the FULL extended quarterly sample (1948Q1-2024Q4), not</t>
+          <t>## Classification</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>appended to the original-window filter output. This avoids endpoint bias on</t>
+          <t>`content_type: time_series` · `construction: composite` · extension applies via</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>the post-2011 segment.</t>
+          <t>re-derivation at quarterly frequency.</t>
         </is>
       </c>
     </row>
@@ -8894,133 +8894,164 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>## No-Proxy disclosure</t>
+          <t>## Method</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>The dead FRED ID `W270RE1Q156NBEA` is replaced by the live pair `W209RC1` +</t>
+          <t>The Hodrick-Prescott (HP) filter (smoothing parameter lambda=100) is applied to the FULL extended quarterly sample (1948Q1-2024Q4), not</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>`GDP` at quarterly frequency. This is a within-FRED routing update to the</t>
+          <t>appended to the original-window filter output. This avoids endpoint bias on</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SAME underlying NIPA Table 1.10 line 2 / line 1 series; not a concept-changing</t>
+          <t>the post-2011 segment.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>substitution. No `proxy: true` flag required.</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>## No-Proxy disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>## No-Synthetic disclosure</t>
+          <t>The dead FRED ID `W270RE1Q156NBEA` is replaced by the live pair `W209RC1` +</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>All quarterly observations are primary BEA/BLS data. HP filtering is the</t>
+          <t>`GDP` at quarterly frequency. This is a within-FRED routing update to the</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>documented analytical method per Shaikh's Appendix 14.2.</t>
+          <t>SAME underlying National Income and Product Accounts (NIPA) Table 1.10 line 2 / line 1 series; not a concept-changing</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>substitution. No `proxy: true` flag required.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>## Failure-mode table</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>| Mode | Trigger | Behaviour |</t>
+          <t>## No-Synthetic disclosure</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>All quarterly observations are primary BEA/BLS data. HP filtering is the</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>| FRED key missing | env unset | Quarterly axes skipped; annual reference axes still emitted |</t>
+          <t>documented analytical method per Shaikh's Appendix 14.2.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>| One quarterly source missing | API outage | Quarterly axes skipped; annual reference axes still emitted |</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>| HP lambda substitution | maintainer error | Caught by Shaikh-specific test (HP_LAMBDA_CH14=100 constant) |</t>
+          <t>## Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>| Mode | Trigger | Behaviour |</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>## CD2 divergence pre-disclosure</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Minor (&lt;2%) divergence expected on the quarterly axes vs CD2 because CD2 used</t>
+          <t>| FRED key missing | env unset | Quarterly axes skipped; annual reference axes still emitted |</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>the now-retired W270RE1Q156NBEA and a different quarterly aggregation</t>
+          <t>| One quarterly source missing | API outage | Quarterly axes skipped; annual reference axes still emitted |</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
+        <is>
+          <t>| HP lambda substitution | maintainer error | Caught by Shaikh-specific test (HP_LAMBDA_CH14=100 constant) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>## Divergence from the predecessor build</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Minor (&lt;2%) divergence expected on the quarterly axes vs the predecessor build because the predecessor build used</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>the now-retired W270RE1Q156NBEA and a different quarterly aggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>convention.</t>
         </is>
@@ -9462,7 +9493,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-18T23:18:45.098691+00:00</t>
+          <t>2026-07-02T13:21:37.309298+00:00</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9505,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{"S1403-WSH_ANNUALAVG_HP100": {"n": 53, "mae": 0.018575490413448418, "max_pct_err": 5.845552222501221, "note": "Annual mean of quarterly HP100 series; expected to differ modestly from annual HP100 of annual data (different filter input + endpoint effects)."}, "S1403-ULINT_ANNUALAVG_HP100": {"n": 64, "mae": 0.01788219488523258, "max_pct_err": 45.82683185153454, "note": "Annual mean of quarterly HP100 series; expected to differ modestly from annual HP100 of annual data (different filter input + endpoint effects)."}}</t>
+          <t>{"S1403-WSH_ANNUALAVG_HP100": {"n": 53, "mae": 0.018575490454150766, "max_pct_err": 5.84555222250088, "note": "Annual mean of quarterly HP100 series; expected to differ modestly from annual HP100 of annual data (different filter input + endpoint effects)."}, "S1403-ULINT_ANNUALAVG_HP100": {"n": 64, "mae": 0.01788219488523258, "max_pct_err": 45.82683185153454, "note": "Annual mean of quarterly HP100 series; expected to differ modestly from annual HP100 of annual data (different filter input + endpoint effects)."}}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1403_extenbook.xlsx
+++ b/extenbooks/S1403_extenbook.xlsx
@@ -9493,7 +9493,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02T13:21:37.309298+00:00</t>
+          <t>2026-07-11T03:44:22.975552+00:00</t>
         </is>
       </c>
     </row>
@@ -9520,11 +9520,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9547,6 +9547,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_14_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>validated_book_and_extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Ch.14 Figure 14.12 (Empirical Path of the Wage Share versus Unemployment Intensity, United States, 1948-2011) -- the empirical analogue of the theoretical Goodwin-type clockwise spiral in Fig 14.9. Real data present in chopped CSV (273 points across 4 subseries); book_period_validated; figure number and quotes KB-verified (Fig 14.12 quote verbatim at ch14 KB line 1442/1450; HP(100) default-parameter method at Appendix 14.2, KB ch18 line 8622). Two reference axes (annual Appendix HP100) plus two FRED-derived quarterly-collapsed axes -- per-subseries units split below.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1403_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1403_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quarterly phase plot per Phase 4 Q1 resolution. Sidecar quarterly parquet at data/processed/_sidecars/S1403_quarterly.parquet. VREF 2026-07-02: quarterly FRED inputs (GDP/W209RC1/UNRATE/UEMPMEAN) refreshed to the LATEST FRED/ALFRED vintage (realtime pin 2026-05-18 -&gt; 2026-07-02) per USER RULING; W209RC1-q 2025Q4 revised 16022.5 -&gt; 15949.5. Book annual-reference rows (S1403-A/B, 1948-2011) byte-identical. The HP(100) recompute shifted S1403-WSH_ANNUALAVG_HP100 only materially at the tail (2025: 0.511136 -&gt; 0.510557, -5.79e-4, -0.113%; 2024: -9.7e-5); pre-2024 shifts are ~1e-15 float ULP. S1403-ULINT unchanged (UNRATE/UEMPMEAN never revised), so validation.reference_values (ref_subseries S1403-ULINT, 2025=0.095978) still holds. V03 PASS. See config/VINTAGE_MANIFEST.json + remediation_campaign/evidence_VREF.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>decimal_hp100_phase_axes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
